--- a/data_raw/exportacion_leche_polvo_entera.xlsx
+++ b/data_raw/exportacion_leche_polvo_entera.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/2- Mercado externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="721" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4723A0B2-0C2D-4BA3-82E2-08AB10AA6CE1}"/>
+  <xr:revisionPtr revIDLastSave="742" documentId="8_{3D899436-D7B7-4A83-875F-059D2530D157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEFE1D74-6DD6-457E-8E65-7C8C842163BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="703" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="85">
   <si>
     <t>Estos datos se consideran preliminares a partir del 23/10/2020 e incluyen Admisiones temporales. Estas modificaciones recientes se deben a cambios realizados por la Agencia de Aduanas de Uruguay.</t>
   </si>
@@ -1804,14 +1804,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3590,7 +3590,9 @@
       <c r="J35" s="100">
         <v>41213979.369999953</v>
       </c>
-      <c r="K35" s="100"/>
+      <c r="K35" s="100">
+        <v>52296745.449999973</v>
+      </c>
       <c r="L35" s="100"/>
       <c r="M35" s="99"/>
       <c r="N35" s="99"/>
@@ -4657,7 +4659,9 @@
       <c r="J59" s="91">
         <v>11081.581000000002</v>
       </c>
-      <c r="K59" s="91"/>
+      <c r="K59" s="91">
+        <v>14101.452479999993</v>
+      </c>
       <c r="L59" s="95"/>
       <c r="M59" s="95"/>
       <c r="N59" s="95"/>
@@ -5742,7 +5746,9 @@
       <c r="J83" s="18">
         <v>3719.1425456349543</v>
       </c>
-      <c r="K83" s="18"/>
+      <c r="K83" s="18">
+        <v>3708.6070051416436</v>
+      </c>
       <c r="L83" s="18"/>
       <c r="M83" s="18"/>
       <c r="N83" s="18"/>
@@ -5908,23 +5914,23 @@
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="128" t="s">
+      <c r="C13" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="129"/>
-      <c r="E13" s="128" t="s">
+      <c r="E13" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="129"/>
-      <c r="G13" s="128" t="s">
+      <c r="G13" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="129"/>
-      <c r="I13" s="128" t="s">
+      <c r="I13" s="133" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="129"/>
-      <c r="K13" s="128" t="s">
+      <c r="K13" s="133" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="129"/>
@@ -6711,8 +6717,12 @@
       <c r="F34" s="54">
         <v>0.28107286975257928</v>
       </c>
-      <c r="G34" s="18"/>
-      <c r="H34" s="54"/>
+      <c r="G34" s="18">
+        <v>42865.030429999984</v>
+      </c>
+      <c r="H34" s="54">
+        <v>-4.7601420240639736E-2</v>
+      </c>
       <c r="I34" s="53"/>
       <c r="J34" s="54"/>
       <c r="K34" s="18"/>
@@ -6730,23 +6740,23 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:12" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="128" t="s">
+      <c r="C37" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="129"/>
-      <c r="E37" s="128" t="s">
+      <c r="E37" s="133" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="129"/>
-      <c r="G37" s="128" t="s">
+      <c r="G37" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H37" s="129"/>
-      <c r="I37" s="128" t="s">
+      <c r="I37" s="133" t="s">
         <v>31</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="128" t="s">
+      <c r="K37" s="133" t="s">
         <v>32</v>
       </c>
       <c r="L37" s="129"/>
@@ -7537,8 +7547,12 @@
       <c r="F58" s="54">
         <v>-9.3127046747667586E-2</v>
       </c>
-      <c r="G58" s="53"/>
-      <c r="H58" s="54"/>
+      <c r="G58" s="53">
+        <v>3747.7552869662095</v>
+      </c>
+      <c r="H58" s="54">
+        <v>-8.3553131062109709E-2</v>
+      </c>
       <c r="I58" s="53"/>
       <c r="J58" s="54"/>
       <c r="K58" s="53"/>
@@ -7589,23 +7603,23 @@
       <c r="B67" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="128" t="s">
+      <c r="C67" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="129"/>
-      <c r="E67" s="128" t="s">
+      <c r="E67" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="130"/>
-      <c r="G67" s="128" t="s">
+      <c r="F67" s="128"/>
+      <c r="G67" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H67" s="129"/>
-      <c r="I67" s="130" t="s">
+      <c r="I67" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J67" s="129"/>
-      <c r="K67" s="130" t="s">
+      <c r="K67" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L67" s="129"/>
@@ -7626,8 +7640,12 @@
       <c r="F68" s="61">
         <v>0.41115705106505651</v>
       </c>
-      <c r="G68" s="60"/>
-      <c r="H68" s="61"/>
+      <c r="G68" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68" s="61">
+        <v>0.34842316223947478</v>
+      </c>
       <c r="I68" s="60"/>
       <c r="J68" s="61"/>
       <c r="K68" s="60"/>
@@ -7649,8 +7667,12 @@
       <c r="F69" s="64">
         <v>0.28617390053916414</v>
       </c>
-      <c r="G69" s="63"/>
-      <c r="H69" s="64"/>
+      <c r="G69" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H69" s="64">
+        <v>0.12487418403743604</v>
+      </c>
       <c r="I69" s="63"/>
       <c r="J69" s="64"/>
       <c r="K69" s="63"/>
@@ -7672,8 +7694,12 @@
       <c r="F70" s="64">
         <v>5.1827652884059092E-2</v>
       </c>
-      <c r="G70" s="63"/>
-      <c r="H70" s="64"/>
+      <c r="G70" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" s="64">
+        <v>6.1972751732996073E-2</v>
+      </c>
       <c r="I70" s="63"/>
       <c r="J70" s="64"/>
       <c r="K70" s="63"/>
@@ -7695,8 +7721,12 @@
       <c r="F71" s="64">
         <v>4.7047697731091499E-2</v>
       </c>
-      <c r="G71" s="63"/>
-      <c r="H71" s="64"/>
+      <c r="G71" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H71" s="64">
+        <v>5.7847505982109526E-2</v>
+      </c>
       <c r="I71" s="63"/>
       <c r="J71" s="64"/>
       <c r="K71" s="63"/>
@@ -7718,8 +7748,12 @@
       <c r="F72" s="71">
         <v>4.2187842352278848E-2</v>
       </c>
-      <c r="G72" s="70"/>
-      <c r="H72" s="71"/>
+      <c r="G72" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="H72" s="71">
+        <v>5.5046948006684443E-2</v>
+      </c>
       <c r="I72" s="70"/>
       <c r="J72" s="71"/>
       <c r="K72" s="70"/>
@@ -7746,23 +7780,23 @@
       <c r="B75" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="128" t="s">
+      <c r="C75" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="129"/>
-      <c r="E75" s="128" t="s">
+      <c r="E75" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="130"/>
-      <c r="G75" s="128" t="s">
+      <c r="F75" s="128"/>
+      <c r="G75" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H75" s="129"/>
-      <c r="I75" s="130" t="s">
+      <c r="I75" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="129"/>
-      <c r="K75" s="130" t="s">
+      <c r="K75" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L75" s="129"/>
@@ -7963,23 +7997,23 @@
       <c r="B83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="128" t="s">
+      <c r="C83" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="129"/>
-      <c r="E83" s="128" t="s">
+      <c r="E83" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="130"/>
-      <c r="G83" s="128" t="s">
+      <c r="F83" s="128"/>
+      <c r="G83" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H83" s="129"/>
-      <c r="I83" s="130" t="s">
+      <c r="I83" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="129"/>
-      <c r="K83" s="130" t="s">
+      <c r="K83" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L83" s="129"/>
@@ -8180,23 +8214,23 @@
       <c r="B91" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="128" t="s">
+      <c r="C91" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="129"/>
-      <c r="E91" s="128" t="s">
+      <c r="E91" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="130"/>
-      <c r="G91" s="128" t="s">
+      <c r="F91" s="128"/>
+      <c r="G91" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H91" s="129"/>
-      <c r="I91" s="130" t="s">
+      <c r="I91" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J91" s="129"/>
-      <c r="K91" s="130" t="s">
+      <c r="K91" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L91" s="129"/>
@@ -8397,23 +8431,23 @@
       <c r="B99" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="128" t="s">
+      <c r="C99" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="129"/>
-      <c r="E99" s="128" t="s">
+      <c r="E99" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="130"/>
-      <c r="G99" s="128" t="s">
+      <c r="F99" s="128"/>
+      <c r="G99" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="129"/>
-      <c r="I99" s="130" t="s">
+      <c r="I99" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J99" s="129"/>
-      <c r="K99" s="130" t="s">
+      <c r="K99" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L99" s="129"/>
@@ -8625,23 +8659,23 @@
       <c r="B108" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="128" t="s">
+      <c r="C108" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="129"/>
-      <c r="E108" s="128" t="s">
+      <c r="E108" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="130"/>
-      <c r="G108" s="128" t="s">
+      <c r="F108" s="128"/>
+      <c r="G108" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H108" s="129"/>
-      <c r="I108" s="130" t="s">
+      <c r="I108" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J108" s="129"/>
-      <c r="K108" s="130" t="s">
+      <c r="K108" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L108" s="129"/>
@@ -8855,23 +8889,23 @@
       <c r="B117" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C117" s="128" t="s">
+      <c r="C117" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="129"/>
-      <c r="E117" s="128" t="s">
+      <c r="E117" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="130"/>
-      <c r="G117" s="128" t="s">
+      <c r="F117" s="128"/>
+      <c r="G117" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H117" s="129"/>
-      <c r="I117" s="130" t="s">
+      <c r="I117" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J117" s="129"/>
-      <c r="K117" s="130" t="s">
+      <c r="K117" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L117" s="129"/>
@@ -9085,23 +9119,23 @@
       <c r="B126" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C126" s="128" t="s">
+      <c r="C126" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="129"/>
-      <c r="E126" s="128" t="s">
+      <c r="E126" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="130"/>
-      <c r="G126" s="128" t="s">
+      <c r="F126" s="128"/>
+      <c r="G126" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H126" s="129"/>
-      <c r="I126" s="130" t="s">
+      <c r="I126" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J126" s="129"/>
-      <c r="K126" s="130" t="s">
+      <c r="K126" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L126" s="129"/>
@@ -9315,23 +9349,23 @@
       <c r="B135" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="128" t="s">
+      <c r="C135" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="129"/>
-      <c r="E135" s="128" t="s">
+      <c r="E135" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F135" s="130"/>
-      <c r="G135" s="128" t="s">
+      <c r="F135" s="128"/>
+      <c r="G135" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H135" s="129"/>
-      <c r="I135" s="130" t="s">
+      <c r="I135" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J135" s="129"/>
-      <c r="K135" s="130" t="s">
+      <c r="K135" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L135" s="129"/>
@@ -9545,23 +9579,23 @@
       <c r="B145" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C145" s="128" t="s">
+      <c r="C145" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="129"/>
-      <c r="E145" s="128" t="s">
+      <c r="E145" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="130"/>
-      <c r="G145" s="128" t="s">
+      <c r="F145" s="128"/>
+      <c r="G145" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H145" s="129"/>
-      <c r="I145" s="130" t="s">
+      <c r="I145" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J145" s="129"/>
-      <c r="K145" s="130" t="s">
+      <c r="K145" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L145" s="129"/>
@@ -9775,23 +9809,23 @@
       <c r="B154" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C154" s="128" t="s">
+      <c r="C154" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="129"/>
-      <c r="E154" s="128" t="s">
+      <c r="E154" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="130"/>
-      <c r="G154" s="128" t="s">
+      <c r="F154" s="128"/>
+      <c r="G154" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H154" s="129"/>
-      <c r="I154" s="130" t="s">
+      <c r="I154" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J154" s="129"/>
-      <c r="K154" s="130" t="s">
+      <c r="K154" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L154" s="129"/>
@@ -10005,23 +10039,23 @@
       <c r="B163" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C163" s="128" t="s">
+      <c r="C163" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D163" s="129"/>
-      <c r="E163" s="128" t="s">
+      <c r="E163" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F163" s="130"/>
-      <c r="G163" s="128" t="s">
+      <c r="F163" s="128"/>
+      <c r="G163" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H163" s="129"/>
-      <c r="I163" s="130" t="s">
+      <c r="I163" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J163" s="129"/>
-      <c r="K163" s="130" t="s">
+      <c r="K163" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L163" s="129"/>
@@ -10225,23 +10259,23 @@
       <c r="B172" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C172" s="128" t="s">
+      <c r="C172" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D172" s="129"/>
-      <c r="E172" s="128" t="s">
+      <c r="E172" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="130"/>
-      <c r="G172" s="128" t="s">
+      <c r="F172" s="128"/>
+      <c r="G172" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H172" s="129"/>
-      <c r="I172" s="130" t="s">
+      <c r="I172" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J172" s="129"/>
-      <c r="K172" s="130" t="s">
+      <c r="K172" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L172" s="129"/>
@@ -10445,23 +10479,23 @@
       <c r="B181" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C181" s="128" t="s">
+      <c r="C181" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D181" s="129"/>
-      <c r="E181" s="128" t="s">
+      <c r="E181" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="130"/>
-      <c r="G181" s="128" t="s">
+      <c r="F181" s="128"/>
+      <c r="G181" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H181" s="129"/>
-      <c r="I181" s="130" t="s">
+      <c r="I181" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J181" s="129"/>
-      <c r="K181" s="130" t="s">
+      <c r="K181" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L181" s="129"/>
@@ -10666,23 +10700,23 @@
       <c r="B190" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C190" s="128" t="s">
+      <c r="C190" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D190" s="129"/>
-      <c r="E190" s="128" t="s">
+      <c r="E190" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F190" s="130"/>
-      <c r="G190" s="128" t="s">
+      <c r="F190" s="128"/>
+      <c r="G190" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H190" s="129"/>
-      <c r="I190" s="130" t="s">
+      <c r="I190" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J190" s="129"/>
-      <c r="K190" s="130" t="s">
+      <c r="K190" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L190" s="129"/>
@@ -10887,23 +10921,23 @@
       <c r="B199" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C199" s="128" t="s">
+      <c r="C199" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D199" s="129"/>
-      <c r="E199" s="128" t="s">
+      <c r="E199" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F199" s="130"/>
-      <c r="G199" s="128" t="s">
+      <c r="F199" s="128"/>
+      <c r="G199" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H199" s="129"/>
-      <c r="I199" s="130" t="s">
+      <c r="I199" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J199" s="129"/>
-      <c r="K199" s="130" t="s">
+      <c r="K199" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L199" s="129"/>
@@ -11108,23 +11142,23 @@
       <c r="B208" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C208" s="128" t="s">
+      <c r="C208" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D208" s="129"/>
-      <c r="E208" s="128" t="s">
+      <c r="E208" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="130"/>
-      <c r="G208" s="128" t="s">
+      <c r="F208" s="128"/>
+      <c r="G208" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H208" s="129"/>
-      <c r="I208" s="130" t="s">
+      <c r="I208" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J208" s="129"/>
-      <c r="K208" s="130" t="s">
+      <c r="K208" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L208" s="129"/>
@@ -11329,23 +11363,23 @@
       <c r="B217" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C217" s="128" t="s">
+      <c r="C217" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D217" s="129"/>
-      <c r="E217" s="128" t="s">
+      <c r="E217" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="130"/>
-      <c r="G217" s="128" t="s">
+      <c r="F217" s="128"/>
+      <c r="G217" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H217" s="129"/>
-      <c r="I217" s="130" t="s">
+      <c r="I217" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J217" s="129"/>
-      <c r="K217" s="130" t="s">
+      <c r="K217" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L217" s="129"/>
@@ -11550,23 +11584,23 @@
       <c r="B226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C226" s="128" t="s">
+      <c r="C226" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D226" s="129"/>
-      <c r="E226" s="128" t="s">
+      <c r="E226" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F226" s="130"/>
-      <c r="G226" s="128" t="s">
+      <c r="F226" s="128"/>
+      <c r="G226" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H226" s="129"/>
-      <c r="I226" s="130" t="s">
+      <c r="I226" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J226" s="129"/>
-      <c r="K226" s="130" t="s">
+      <c r="K226" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L226" s="129"/>
@@ -11754,7 +11788,7 @@
     </row>
     <row r="233" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="234" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="133" t="s">
+      <c r="C234" s="130" t="s">
         <v>73</v>
       </c>
       <c r="D234" s="131"/>
@@ -11771,23 +11805,23 @@
       <c r="B235" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C235" s="128" t="s">
+      <c r="C235" s="133" t="s">
         <v>28</v>
       </c>
       <c r="D235" s="129"/>
-      <c r="E235" s="128" t="s">
+      <c r="E235" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="F235" s="130"/>
-      <c r="G235" s="128" t="s">
+      <c r="F235" s="128"/>
+      <c r="G235" s="133" t="s">
         <v>30</v>
       </c>
       <c r="H235" s="129"/>
-      <c r="I235" s="130" t="s">
+      <c r="I235" s="128" t="s">
         <v>31</v>
       </c>
       <c r="J235" s="129"/>
-      <c r="K235" s="130" t="s">
+      <c r="K235" s="128" t="s">
         <v>17</v>
       </c>
       <c r="L235" s="129"/>
@@ -11975,24 +12009,95 @@
     </row>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="C216:L216"/>
-    <mergeCell ref="C234:L234"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="E226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="C134:L134"/>
+    <mergeCell ref="C125:L125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="C153:L153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C171:L171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="K172:L172"/>
     <mergeCell ref="C180:L180"/>
     <mergeCell ref="C181:D181"/>
     <mergeCell ref="E181:F181"/>
@@ -12017,95 +12122,24 @@
     <mergeCell ref="C208:D208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="G208:H208"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C171:L171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="K172:L172"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="C153:L153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="C134:L134"/>
-    <mergeCell ref="C125:L125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="C216:L216"/>
+    <mergeCell ref="C234:L234"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="K226:L226"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12114,7 +12148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B9:I249"/>
+  <dimension ref="B9:I250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -15454,21 +15488,35 @@
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B248" s="107">
+      <c r="B248" s="93">
         <v>46235</v>
       </c>
-      <c r="C248" s="105">
+      <c r="C248" s="87">
         <v>41213979.369999953</v>
       </c>
-      <c r="D248" s="21">
+      <c r="D248" s="83">
         <v>11081.581000000002</v>
       </c>
-      <c r="E248" s="20">
+      <c r="E248" s="22">
         <v>3719.1425456349543</v>
       </c>
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B249" s="55" t="s">
+      <c r="B249" s="107">
+        <v>46266</v>
+      </c>
+      <c r="C249" s="105">
+        <v>52296745.449999973</v>
+      </c>
+      <c r="D249" s="21">
+        <v>14101.452479999993</v>
+      </c>
+      <c r="E249" s="20">
+        <v>3708.6070051416436</v>
+      </c>
+    </row>
+    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B250" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15486,10 +15534,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -15730,35 +15794,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC8F936-4AF3-4FF9-8B1E-0736929643E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15777,21 +15836,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A63F2-73A4-4411-850D-5A778E7E8365}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22D8E8C4-402A-4BF8-8B26-7B3500893BCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0A23CF-A2F5-43F0-A696-7B0E490DFCE8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>